--- a/reports/service-tracking-report-DUANE-NICO-CAWALING-evaluator-cache-serviceTracking-DUANE-NICO-CAWALING-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-DUANE-NICO-CAWALING-evaluator-cache-serviceTracking-DUANE-NICO-CAWALING-IX-202501-202612.xlsx
@@ -10,6 +10,7 @@
     <x:sheet name="August 2025" sheetId="8" r:id="rId8"/>
     <x:sheet name="November 2025" sheetId="9" r:id="rId9"/>
     <x:sheet name="February 2026" sheetId="10" r:id="rId10"/>
+    <x:sheet name="March 2026" sheetId="11" r:id="rId11"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -217,6 +218,24 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1330-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Retailer/Reseller Permit (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HIGH-SPEED MOTORCYCLE PARTS AND ACCESSORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Purok Pines 2, Sanito, Ipil (Capital), Zamboanga Sibugay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIX-06354-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1355-880</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -537,7 +556,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -609,6 +628,9 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="14" fontId="11" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -6170,4 +6192,1255 @@
   </x:headerFooter>
   <x:tableParts count="0"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="0" summaryRight="0"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:AB993"/>
+  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
+    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
+    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A1" s="1" t="s"/>
+      <x:c r="B1" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28">
+      <x:c r="A3" s="2" t="s"/>
+      <x:c r="B3" s="2">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s"/>
+      <x:c r="D3" s="2" t="s"/>
+      <x:c r="E3" s="2" t="s"/>
+      <x:c r="F3" s="2" t="s"/>
+      <x:c r="G3" s="2" t="s"/>
+      <x:c r="H3" s="2" t="s"/>
+      <x:c r="I3" s="2" t="s"/>
+      <x:c r="J3" s="2" t="s"/>
+      <x:c r="K3" s="2" t="s"/>
+      <x:c r="L3" s="2" t="s"/>
+      <x:c r="M3" s="2" t="s"/>
+      <x:c r="N3" s="2" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28">
+      <x:c r="A4" s="2" t="s"/>
+      <x:c r="B4" s="2" t="s"/>
+      <x:c r="C4" s="2" t="s"/>
+      <x:c r="D4" s="2" t="s"/>
+      <x:c r="E4" s="2" t="s"/>
+      <x:c r="F4" s="2" t="s"/>
+      <x:c r="G4" s="2" t="s"/>
+      <x:c r="H4" s="2" t="s"/>
+      <x:c r="I4" s="2" t="s"/>
+      <x:c r="J4" s="2" t="s"/>
+      <x:c r="K4" s="2" t="s"/>
+      <x:c r="L4" s="2" t="s"/>
+      <x:c r="M4" s="2" t="s"/>
+      <x:c r="N4" s="2" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A5" s="3" t="s"/>
+      <x:c r="B5" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D5" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E5" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F5" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G5" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H5" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I5" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J5" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K5" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L5" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M5" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N5" s="3" t="s"/>
+      <x:c r="O5" s="6" t="s"/>
+      <x:c r="P5" s="6" t="s"/>
+      <x:c r="Q5" s="6" t="s"/>
+      <x:c r="R5" s="6" t="s"/>
+      <x:c r="S5" s="6" t="s"/>
+      <x:c r="T5" s="6" t="s"/>
+      <x:c r="U5" s="6" t="s"/>
+      <x:c r="V5" s="6" t="s"/>
+      <x:c r="W5" s="6" t="s"/>
+      <x:c r="X5" s="6" t="s"/>
+      <x:c r="Y5" s="6" t="s"/>
+      <x:c r="Z5" s="6" t="s"/>
+      <x:c r="AA5" s="6" t="s"/>
+      <x:c r="AB5" s="6" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A6" s="7" t="s"/>
+      <x:c r="B6" s="11" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H6" s="12">
+        <x:v>46076.245</x:v>
+      </x:c>
+      <x:c r="I6" s="12">
+        <x:v>46076.2450115741</x:v>
+      </x:c>
+      <x:c r="J6" s="11" t="n">
+        <x:v>1216190</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L6" s="12">
+        <x:v>46094.1710416667</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="N6" s="7" t="s"/>
+      <x:c r="O6" s="9" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A7" s="7" t="s"/>
+      <x:c r="B7" s="8" t="s"/>
+      <x:c r="C7" s="8" t="s"/>
+      <x:c r="D7" s="8" t="s"/>
+      <x:c r="E7" s="8" t="s"/>
+      <x:c r="F7" s="8" t="s"/>
+      <x:c r="G7" s="8" t="s"/>
+      <x:c r="H7" s="8" t="s"/>
+      <x:c r="I7" s="8" t="s"/>
+      <x:c r="J7" s="8" t="s"/>
+      <x:c r="K7" s="8" t="s"/>
+      <x:c r="L7" s="8" t="s"/>
+      <x:c r="M7" s="8" t="s"/>
+      <x:c r="N7" s="7" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C9" s="16" t="s"/>
+      <x:c r="D9" s="16" t="s"/>
+      <x:c r="E9" s="17" t="s"/>
+      <x:c r="F9" s="17" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B10" s="18" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C10" s="19" t="s"/>
+      <x:c r="D10" s="19" t="s"/>
+      <x:c r="E10" s="19" t="s"/>
+      <x:c r="F10" s="20" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B11" s="21" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C11" s="22" t="s"/>
+      <x:c r="D11" s="22" t="s"/>
+      <x:c r="E11" s="22" t="s"/>
+      <x:c r="F11" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B12" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C12" s="25" t="s"/>
+      <x:c r="D12" s="25" t="s"/>
+      <x:c r="E12" s="25" t="s"/>
+      <x:c r="F12" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
+  </x:sheetData>
+  <x:mergeCells count="6">
+    <x:mergeCell ref="B1:M2"/>
+    <x:mergeCell ref="B3:M3"/>
+    <x:mergeCell ref="B9:F9"/>
+    <x:mergeCell ref="B10:E10"/>
+    <x:mergeCell ref="B11:E11"/>
+    <x:mergeCell ref="B12:E12"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader/>
+    <x:oddFooter/>
+    <x:evenHeader/>
+    <x:evenFooter/>
+    <x:firstHeader/>
+    <x:firstFooter/>
+  </x:headerFooter>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>
--- a/reports/service-tracking-report-DUANE-NICO-CAWALING-evaluator-cache-serviceTracking-DUANE-NICO-CAWALING-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-DUANE-NICO-CAWALING-evaluator-cache-serviceTracking-DUANE-NICO-CAWALING-IX-202501-202612.xlsx
@@ -13,58 +13,22 @@
     <x:sheet name="March 2026" sheetId="11" r:id="rId11"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
@@ -245,7 +209,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -272,12 +236,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -288,16 +246,30 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -321,7 +293,15 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="18"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
   </x:fonts>
@@ -347,8 +327,19 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="14">
+  <x:borders count="17">
     <x:border/>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+    </x:border>
     <x:border>
       <x:left style="thin">
         <x:color rgb="FF000000"/>
@@ -364,17 +355,6 @@
       <x:left style="thin">
         <x:color rgb="FF000000"/>
       </x:left>
-      <x:right style="thin">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
@@ -555,8 +535,59 @@
         <x:color rgb="FF000000"/>
       </x:diagonal>
     </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thick">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thick">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -567,79 +598,103 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="14" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="15" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="16" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="41">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
@@ -647,114 +702,143 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -1017,224 +1101,226 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45839</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>17</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>45860.0993981482</x:v>
       </x:c>
-      <x:c r="I6" s="13">
+      <x:c r="I6" s="14">
         <x:v>45853</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="n">
+      <x:c r="J6" s="12" t="n">
         <x:v>1346409</x:v>
       </x:c>
-      <x:c r="K6" s="14" t="n">
+      <x:c r="K6" s="15" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="16">
         <x:v>45860.1449537037</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s"/>
-      <x:c r="E7" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s"/>
+      <x:c r="E7" s="17" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
         <x:v>45861.1130439815</x:v>
       </x:c>
-      <x:c r="I7" s="12">
+      <x:c r="I7" s="18">
         <x:v>45861.1130555556</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="n">
+      <x:c r="J7" s="17" t="n">
         <x:v>1346412</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="n">
+      <x:c r="K7" s="19" t="n">
         <x:v>930</x:v>
       </x:c>
-      <x:c r="L7" s="12">
+      <x:c r="L7" s="18">
         <x:v>45862.3035648148</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="M7" s="17" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C10" s="16" t="s"/>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="17" t="s"/>
-      <x:c r="F10" s="17" t="s"/>
+      <x:c r="B10" s="20" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="21" t="s"/>
+      <x:c r="D10" s="21" t="s"/>
+      <x:c r="E10" s="22" t="s"/>
+      <x:c r="F10" s="22" t="s"/>
     </x:row>
     <x:row r="11" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="20" t="s">
-        <x:v>27</x:v>
+      <x:c r="B11" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="24" t="s"/>
+      <x:c r="D11" s="24" t="s"/>
+      <x:c r="E11" s="24" t="s"/>
+      <x:c r="F11" s="25" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="n">
+      <x:c r="B12" s="26" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s"/>
+      <x:c r="D12" s="27" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="n">
+      <x:c r="B13" s="26" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s"/>
+      <x:c r="D13" s="27" t="s"/>
+      <x:c r="E13" s="27" t="s"/>
+      <x:c r="F13" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
+      <x:c r="B14" s="29" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C14" s="30" t="s"/>
+      <x:c r="D14" s="30" t="s"/>
+      <x:c r="E14" s="30" t="s"/>
+      <x:c r="F14" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -2301,275 +2387,264 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45870</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>29</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>31</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>32</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>45881.2688541667</x:v>
       </x:c>
-      <x:c r="I6" s="13">
+      <x:c r="I6" s="14">
         <x:v>45927</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="n">
+      <x:c r="J6" s="12" t="n">
         <x:v>1346458</x:v>
       </x:c>
-      <x:c r="K6" s="14" t="n">
+      <x:c r="K6" s="15" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="16">
         <x:v>45882.0237847222</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
+      <x:c r="D7" s="17" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E7" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
         <x:v>45870.3069328704</x:v>
       </x:c>
-      <x:c r="I7" s="13">
+      <x:c r="I7" s="32">
         <x:v>46186</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="n">
+      <x:c r="J7" s="17" t="n">
         <x:v>1346441</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="n">
+      <x:c r="K7" s="19" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L7" s="12">
+      <x:c r="L7" s="18">
         <x:v>45883.1603356482</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="M7" s="17" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="27" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C8" s="27" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D8" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="27" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F8" s="27" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="G8" s="27" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H8" s="29">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="33" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C8" s="33" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D8" s="33" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="33" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F8" s="33" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G8" s="33" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H8" s="34">
         <x:v>45881.2806365741</x:v>
       </x:c>
-      <x:c r="I8" s="30">
+      <x:c r="I8" s="35">
         <x:v>45892</x:v>
       </x:c>
-      <x:c r="J8" s="28" t="n">
+      <x:c r="J8" s="33" t="n">
         <x:v>1346470</x:v>
       </x:c>
-      <x:c r="K8" s="31" t="n">
+      <x:c r="K8" s="36" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L8" s="32">
+      <x:c r="L8" s="34">
         <x:v>45883.2976041667</x:v>
       </x:c>
-      <x:c r="M8" s="27" t="s">
-        <x:v>19</x:v>
+      <x:c r="M8" s="33" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s"/>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="17" t="s"/>
-      <x:c r="F11" s="17" t="s"/>
+      <x:c r="B11" s="20" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="21" t="s"/>
+      <x:c r="D11" s="21" t="s"/>
+      <x:c r="E11" s="22" t="s"/>
+      <x:c r="F11" s="22" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="18" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="s"/>
-      <x:c r="D12" s="19" t="s"/>
-      <x:c r="E12" s="19" t="s"/>
-      <x:c r="F12" s="20" t="s">
-        <x:v>27</x:v>
+      <x:c r="B12" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="24" t="s"/>
+      <x:c r="D12" s="24" t="s"/>
+      <x:c r="E12" s="24" t="s"/>
+      <x:c r="F12" s="25" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="n">
+      <x:c r="B13" s="26" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s"/>
+      <x:c r="D13" s="27" t="s"/>
+      <x:c r="E13" s="27" t="s"/>
+      <x:c r="F13" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="21" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="23" t="n">
+      <x:c r="B14" s="26" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="21" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C15" s="22" t="s"/>
-      <x:c r="D15" s="22" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="23" t="n">
+      <x:c r="B15" s="26" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C16" s="25" t="s"/>
-      <x:c r="D16" s="25" t="s"/>
-      <x:c r="E16" s="25" t="s"/>
-      <x:c r="F16" s="26" t="n">
+      <x:c r="B16" s="29" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -3635,273 +3710,262 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45962</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>44</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s"/>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s"/>
       <x:c r="E6" s="11" t="s">
-        <x:v>46</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>47</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>45951.1032638889</x:v>
       </x:c>
-      <x:c r="I6" s="12">
+      <x:c r="I6" s="13">
         <x:v>45951.103287037</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="n">
+      <x:c r="J6" s="12" t="n">
         <x:v>1346752</x:v>
       </x:c>
-      <x:c r="K6" s="14" t="n">
+      <x:c r="K6" s="15" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="16">
         <x:v>45971.0888194444</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="17" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
         <x:v>45980.2160416667</x:v>
       </x:c>
-      <x:c r="I7" s="13">
+      <x:c r="I7" s="32">
         <x:v>45979</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="n">
+      <x:c r="J7" s="17" t="n">
         <x:v>1346786</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="n">
+      <x:c r="K7" s="19" t="n">
         <x:v>5280</x:v>
       </x:c>
-      <x:c r="L7" s="12">
+      <x:c r="L7" s="18">
         <x:v>45985.3594791667</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="M7" s="17" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="27" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D8" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="27" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F8" s="27" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G8" s="27" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H8" s="29">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="33" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="33" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D8" s="33" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="33" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F8" s="33" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G8" s="33" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H8" s="34">
         <x:v>45959.0699074074</x:v>
       </x:c>
-      <x:c r="I8" s="30">
+      <x:c r="I8" s="35">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J8" s="28" t="n">
+      <x:c r="J8" s="33" t="n">
         <x:v>1346761</x:v>
       </x:c>
-      <x:c r="K8" s="31" t="n">
+      <x:c r="K8" s="36" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="32">
+      <x:c r="L8" s="34">
         <x:v>45972.2719560185</x:v>
       </x:c>
-      <x:c r="M8" s="27" t="s">
-        <x:v>19</x:v>
+      <x:c r="M8" s="33" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s"/>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="17" t="s"/>
-      <x:c r="F11" s="17" t="s"/>
+      <x:c r="B11" s="20" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="21" t="s"/>
+      <x:c r="D11" s="21" t="s"/>
+      <x:c r="E11" s="22" t="s"/>
+      <x:c r="F11" s="22" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="18" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="s"/>
-      <x:c r="D12" s="19" t="s"/>
-      <x:c r="E12" s="19" t="s"/>
-      <x:c r="F12" s="20" t="s">
-        <x:v>27</x:v>
+      <x:c r="B12" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="24" t="s"/>
+      <x:c r="D12" s="24" t="s"/>
+      <x:c r="E12" s="24" t="s"/>
+      <x:c r="F12" s="25" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="n">
+      <x:c r="B13" s="26" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s"/>
+      <x:c r="D13" s="27" t="s"/>
+      <x:c r="E13" s="27" t="s"/>
+      <x:c r="F13" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="21" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="23" t="n">
+      <x:c r="B14" s="26" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="22" t="s"/>
-      <x:c r="D15" s="22" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="23" t="n">
+      <x:c r="B15" s="26" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C16" s="25" t="s"/>
-      <x:c r="D16" s="25" t="s"/>
-      <x:c r="E16" s="25" t="s"/>
-      <x:c r="F16" s="26" t="n">
+      <x:c r="B16" s="29" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -4967,226 +5031,228 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>29</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>57</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>46057.234375</x:v>
       </x:c>
-      <x:c r="I6" s="13">
+      <x:c r="I6" s="14">
         <x:v>41712</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="n">
+      <x:c r="J6" s="12" t="n">
         <x:v>1216128</x:v>
       </x:c>
-      <x:c r="K6" s="14" t="n">
+      <x:c r="K6" s="15" t="n">
         <x:v>630</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="16">
         <x:v>46072.0668055556</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="17" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
+      <x:c r="F7" s="17" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
         <x:v>46066.3781828704</x:v>
       </x:c>
-      <x:c r="I7" s="13">
+      <x:c r="I7" s="32">
         <x:v>46081</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="n">
+      <x:c r="J7" s="17" t="n">
         <x:v>1346991</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="n">
+      <x:c r="K7" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L7" s="12">
+      <x:c r="L7" s="18">
         <x:v>46077.0856712963</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="M7" s="17" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C10" s="16" t="s"/>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="17" t="s"/>
-      <x:c r="F10" s="17" t="s"/>
+      <x:c r="B10" s="20" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="21" t="s"/>
+      <x:c r="D10" s="21" t="s"/>
+      <x:c r="E10" s="22" t="s"/>
+      <x:c r="F10" s="22" t="s"/>
     </x:row>
     <x:row r="11" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="20" t="s">
-        <x:v>27</x:v>
+      <x:c r="B11" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="24" t="s"/>
+      <x:c r="D11" s="24" t="s"/>
+      <x:c r="E11" s="24" t="s"/>
+      <x:c r="F11" s="25" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="n">
+      <x:c r="B12" s="26" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s"/>
+      <x:c r="D12" s="27" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="n">
+      <x:c r="B13" s="26" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s"/>
+      <x:c r="D13" s="27" t="s"/>
+      <x:c r="E13" s="27" t="s"/>
+      <x:c r="F13" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
+      <x:c r="B14" s="29" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C14" s="30" t="s"/>
+      <x:c r="D14" s="30" t="s"/>
+      <x:c r="E14" s="30" t="s"/>
+      <x:c r="F14" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -6253,190 +6319,186 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>64</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>67</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>68</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>46076.245</x:v>
       </x:c>
-      <x:c r="I6" s="12">
+      <x:c r="I6" s="13">
         <x:v>46076.2450115741</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="n">
+      <x:c r="J6" s="12" t="n">
         <x:v>1216190</x:v>
       </x:c>
-      <x:c r="K6" s="14" t="n">
+      <x:c r="K6" s="15" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="16">
         <x:v>46094.1710416667</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="37" t="s"/>
+      <x:c r="C7" s="37" t="s"/>
+      <x:c r="D7" s="37" t="s"/>
+      <x:c r="E7" s="37" t="s"/>
+      <x:c r="F7" s="37" t="s"/>
+      <x:c r="G7" s="37" t="s"/>
+      <x:c r="H7" s="37" t="s"/>
+      <x:c r="I7" s="37" t="s"/>
+      <x:c r="J7" s="37" t="s"/>
+      <x:c r="K7" s="37" t="s"/>
+      <x:c r="L7" s="37" t="s"/>
+      <x:c r="M7" s="37" t="s"/>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C9" s="16" t="s"/>
-      <x:c r="D9" s="16" t="s"/>
-      <x:c r="E9" s="17" t="s"/>
-      <x:c r="F9" s="17" t="s"/>
+      <x:c r="B9" s="38" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="39" t="s"/>
+      <x:c r="D9" s="39" t="s"/>
+      <x:c r="E9" s="40" t="s"/>
+      <x:c r="F9" s="40" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="18" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C10" s="19" t="s"/>
-      <x:c r="D10" s="19" t="s"/>
-      <x:c r="E10" s="19" t="s"/>
-      <x:c r="F10" s="20" t="s">
-        <x:v>27</x:v>
+      <x:c r="B10" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="24" t="s"/>
+      <x:c r="D10" s="24" t="s"/>
+      <x:c r="E10" s="24" t="s"/>
+      <x:c r="F10" s="25" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="21" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C11" s="22" t="s"/>
-      <x:c r="D11" s="22" t="s"/>
-      <x:c r="E11" s="22" t="s"/>
-      <x:c r="F11" s="23" t="n">
+      <x:c r="B11" s="26" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C11" s="27" t="s"/>
+      <x:c r="D11" s="27" t="s"/>
+      <x:c r="E11" s="27" t="s"/>
+      <x:c r="F11" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C12" s="25" t="s"/>
-      <x:c r="D12" s="25" t="s"/>
-      <x:c r="E12" s="25" t="s"/>
-      <x:c r="F12" s="26" t="n">
+      <x:c r="B12" s="29" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C12" s="30" t="s"/>
+      <x:c r="D12" s="30" t="s"/>
+      <x:c r="E12" s="30" t="s"/>
+      <x:c r="F12" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-DUANE-NICO-CAWALING-evaluator-cache-serviceTracking-DUANE-NICO-CAWALING-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-DUANE-NICO-CAWALING-evaluator-cache-serviceTracking-DUANE-NICO-CAWALING-IX-202501-202612.xlsx
@@ -1067,7 +1067,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -1137,7 +1137,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>9</x:v>
@@ -2356,7 +2356,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -2426,7 +2426,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>23</x:v>
@@ -3695,7 +3695,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -3763,7 +3763,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>38</x:v>
@@ -5032,7 +5032,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -5102,7 +5102,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>38</x:v>
@@ -6323,7 +6323,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -6393,7 +6393,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="39" t="s"/>
       <x:c r="C7" s="39" t="s"/>

--- a/reports/service-tracking-report-DUANE-NICO-CAWALING-evaluator-cache-serviceTracking-DUANE-NICO-CAWALING-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-DUANE-NICO-CAWALING-evaluator-cache-serviceTracking-DUANE-NICO-CAWALING-IX-202501-202612.xlsx
@@ -26,12 +26,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>DUANE NICO CAWALING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
@@ -212,7 +248,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -257,22 +293,14 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -296,7 +324,7 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
   </x:fonts>
@@ -531,7 +559,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="30">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -542,10 +570,16 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -557,71 +591,53 @@
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="40">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -652,124 +668,96 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -1069,18 +1057,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1098,164 +1074,176 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45860.0993981482</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>45853</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1346409</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>45860.1449537037</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C7" s="17" t="s">
+      <x:c r="J7" s="10" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D7" s="17" t="s"/>
-      <x:c r="E7" s="17" t="s">
+      <x:c r="K7" s="10" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="F7" s="17" t="s">
+      <x:c r="L7" s="10" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="G7" s="17" t="s">
+      <x:c r="M7" s="10" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
-        <x:v>45861.1130439815</x:v>
-      </x:c>
-      <x:c r="I7" s="18">
-        <x:v>45861.1130555556</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1346412</x:v>
-      </x:c>
-      <x:c r="K7" s="19" t="n">
-        <x:v>930</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>45862.3035648148</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
-        <x:v>8</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="20" t="s"/>
-      <x:c r="C8" s="20" t="s"/>
-      <x:c r="D8" s="20" t="s"/>
-      <x:c r="E8" s="20" t="s"/>
-      <x:c r="F8" s="20" t="s"/>
-      <x:c r="G8" s="20" t="s"/>
-      <x:c r="H8" s="20" t="s"/>
-      <x:c r="I8" s="20" t="s"/>
-      <x:c r="J8" s="20" t="s"/>
-      <x:c r="K8" s="20" t="s"/>
-      <x:c r="L8" s="20" t="s"/>
-      <x:c r="M8" s="20" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45860.0993981482</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>45853</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1346409</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45860.1449537037</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="20" t="s"/>
-      <x:c r="C9" s="20" t="s"/>
-      <x:c r="D9" s="20" t="s"/>
-      <x:c r="E9" s="20" t="s"/>
-      <x:c r="F9" s="20" t="s"/>
-      <x:c r="G9" s="20" t="s"/>
-      <x:c r="H9" s="20" t="s"/>
-      <x:c r="I9" s="20" t="s"/>
-      <x:c r="J9" s="20" t="s"/>
-      <x:c r="K9" s="20" t="s"/>
-      <x:c r="L9" s="20" t="s"/>
-      <x:c r="M9" s="20" t="s"/>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s"/>
+      <x:c r="E9" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45861.1130439815</x:v>
+      </x:c>
+      <x:c r="I9" s="12">
+        <x:v>45861.1130555556</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1346412</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>930</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45862.3035648148</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="23" t="s"/>
-      <x:c r="F12" s="23" t="s"/>
+      <x:c r="B12" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C12" s="16" t="s"/>
+      <x:c r="D12" s="16" t="s"/>
+      <x:c r="E12" s="17" t="s"/>
+      <x:c r="F12" s="17" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="s">
-        <x:v>16</x:v>
+      <x:c r="B13" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C13" s="19" t="s"/>
+      <x:c r="D13" s="19" t="s"/>
+      <x:c r="E13" s="19" t="s"/>
+      <x:c r="F13" s="20" t="s">
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="B14" s="21" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="s"/>
+      <x:c r="D14" s="22" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="27" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C15" s="28" t="s"/>
-      <x:c r="D15" s="28" t="s"/>
-      <x:c r="E15" s="28" t="s"/>
-      <x:c r="F15" s="29" t="n">
+      <x:c r="B15" s="21" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="s"/>
+      <x:c r="D15" s="22" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C16" s="31" t="s"/>
-      <x:c r="D16" s="31" t="s"/>
-      <x:c r="E16" s="31" t="s"/>
-      <x:c r="F16" s="32" t="n">
+      <x:c r="B16" s="24" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="s"/>
+      <x:c r="D16" s="25" t="s"/>
+      <x:c r="E16" s="25" t="s"/>
+      <x:c r="F16" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -2358,18 +2346,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2387,215 +2363,227 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45881.2688541667</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>45927</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1346458</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>45882.0237847222</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C7" s="17" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E7" s="17" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="G7" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
-        <x:v>45870.3069328704</x:v>
-      </x:c>
-      <x:c r="I7" s="33">
-        <x:v>46186</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1346441</x:v>
-      </x:c>
-      <x:c r="K7" s="19" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>45883.1603356482</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
-        <x:v>8</x:v>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="34" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C8" s="34" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D8" s="34" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E8" s="34" t="s">
+      <x:c r="B8" s="11" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F8" s="34" t="s">
+      <x:c r="C8" s="11" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G8" s="34" t="s">
+      <x:c r="D8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H8" s="35">
+      <x:c r="F8" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45881.2688541667</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>45927</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1346458</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45882.0237847222</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45870.3069328704</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>46186</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1346441</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45883.1603356482</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="27" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C10" s="27" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D10" s="28" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="27" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F10" s="27" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G10" s="27" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H10" s="29">
         <x:v>45881.2806365741</x:v>
       </x:c>
-      <x:c r="I8" s="36">
+      <x:c r="I10" s="30">
         <x:v>45892</x:v>
       </x:c>
-      <x:c r="J8" s="34" t="n">
+      <x:c r="J10" s="28" t="n">
         <x:v>1346470</x:v>
       </x:c>
-      <x:c r="K8" s="37" t="n">
+      <x:c r="K10" s="31" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L8" s="35">
+      <x:c r="L10" s="32">
         <x:v>45883.2976041667</x:v>
       </x:c>
-      <x:c r="M8" s="34" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="20" t="s"/>
-      <x:c r="C9" s="20" t="s"/>
-      <x:c r="D9" s="20" t="s"/>
-      <x:c r="E9" s="20" t="s"/>
-      <x:c r="F9" s="20" t="s"/>
-      <x:c r="G9" s="20" t="s"/>
-      <x:c r="H9" s="20" t="s"/>
-      <x:c r="I9" s="20" t="s"/>
-      <x:c r="J9" s="20" t="s"/>
-      <x:c r="K9" s="20" t="s"/>
-      <x:c r="L9" s="20" t="s"/>
-      <x:c r="M9" s="20" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B10" s="38" t="s"/>
-      <x:c r="C10" s="38" t="s"/>
-      <x:c r="D10" s="38" t="s"/>
-      <x:c r="E10" s="38" t="s"/>
-      <x:c r="F10" s="38" t="s"/>
-      <x:c r="G10" s="38" t="s"/>
-      <x:c r="H10" s="38" t="s"/>
-      <x:c r="I10" s="38" t="s"/>
-      <x:c r="J10" s="38" t="s"/>
-      <x:c r="K10" s="38" t="s"/>
-      <x:c r="L10" s="38" t="s"/>
-      <x:c r="M10" s="38" t="s"/>
+      <x:c r="M10" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="23" t="s"/>
-      <x:c r="F13" s="23" t="s"/>
+      <x:c r="B13" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C13" s="16" t="s"/>
+      <x:c r="D13" s="16" t="s"/>
+      <x:c r="E13" s="17" t="s"/>
+      <x:c r="F13" s="17" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="s">
-        <x:v>16</x:v>
+      <x:c r="B14" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C14" s="19" t="s"/>
+      <x:c r="D14" s="19" t="s"/>
+      <x:c r="E14" s="19" t="s"/>
+      <x:c r="F14" s="20" t="s">
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="27" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C15" s="28" t="s"/>
-      <x:c r="D15" s="28" t="s"/>
-      <x:c r="E15" s="28" t="s"/>
-      <x:c r="F15" s="29" t="n">
+      <x:c r="B15" s="21" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="s"/>
+      <x:c r="D15" s="22" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="27" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
+      <x:c r="B16" s="21" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C16" s="22" t="s"/>
+      <x:c r="D16" s="22" t="s"/>
+      <x:c r="E16" s="22" t="s"/>
+      <x:c r="F16" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="27" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C17" s="28" t="s"/>
-      <x:c r="D17" s="28" t="s"/>
-      <x:c r="E17" s="28" t="s"/>
-      <x:c r="F17" s="29" t="n">
+      <x:c r="B17" s="21" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C17" s="22" t="s"/>
+      <x:c r="D17" s="22" t="s"/>
+      <x:c r="E17" s="22" t="s"/>
+      <x:c r="F17" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C18" s="31" t="s"/>
-      <x:c r="D18" s="31" t="s"/>
-      <x:c r="E18" s="31" t="s"/>
-      <x:c r="F18" s="32" t="n">
+      <x:c r="B18" s="24" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C18" s="25" t="s"/>
+      <x:c r="D18" s="25" t="s"/>
+      <x:c r="E18" s="25" t="s"/>
+      <x:c r="F18" s="26" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -3697,18 +3685,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3726,213 +3702,225 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45951.1032638889</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45951.103287037</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1346752</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>45971.0888194444</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="17" t="s">
+      <x:c r="D7" s="10" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="17" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
-        <x:v>45980.2160416667</x:v>
-      </x:c>
-      <x:c r="I7" s="33">
-        <x:v>45979</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1346786</x:v>
-      </x:c>
-      <x:c r="K7" s="19" t="n">
-        <x:v>5280</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>45985.3594791667</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="34" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="34" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="34" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E8" s="34" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F8" s="34" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H8" s="35">
+      <x:c r="B8" s="11" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s"/>
+      <x:c r="E8" s="11" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45951.1032638889</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>45951.103287037</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1346752</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45971.0888194444</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45980.2160416667</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>45979</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1346786</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>5280</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45985.3594791667</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="27" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="27" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D10" s="28" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="27" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F10" s="27" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G10" s="27" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H10" s="29">
         <x:v>45959.0699074074</x:v>
       </x:c>
-      <x:c r="I8" s="36">
+      <x:c r="I10" s="30">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J8" s="34" t="n">
+      <x:c r="J10" s="28" t="n">
         <x:v>1346761</x:v>
       </x:c>
-      <x:c r="K8" s="37" t="n">
+      <x:c r="K10" s="31" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="35">
+      <x:c r="L10" s="32">
         <x:v>45972.2719560185</x:v>
       </x:c>
-      <x:c r="M8" s="34" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="20" t="s"/>
-      <x:c r="C9" s="20" t="s"/>
-      <x:c r="D9" s="20" t="s"/>
-      <x:c r="E9" s="20" t="s"/>
-      <x:c r="F9" s="20" t="s"/>
-      <x:c r="G9" s="20" t="s"/>
-      <x:c r="H9" s="20" t="s"/>
-      <x:c r="I9" s="20" t="s"/>
-      <x:c r="J9" s="20" t="s"/>
-      <x:c r="K9" s="20" t="s"/>
-      <x:c r="L9" s="20" t="s"/>
-      <x:c r="M9" s="20" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B10" s="38" t="s"/>
-      <x:c r="C10" s="38" t="s"/>
-      <x:c r="D10" s="38" t="s"/>
-      <x:c r="E10" s="38" t="s"/>
-      <x:c r="F10" s="38" t="s"/>
-      <x:c r="G10" s="38" t="s"/>
-      <x:c r="H10" s="38" t="s"/>
-      <x:c r="I10" s="38" t="s"/>
-      <x:c r="J10" s="38" t="s"/>
-      <x:c r="K10" s="38" t="s"/>
-      <x:c r="L10" s="38" t="s"/>
-      <x:c r="M10" s="38" t="s"/>
+      <x:c r="M10" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="23" t="s"/>
-      <x:c r="F13" s="23" t="s"/>
+      <x:c r="B13" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C13" s="16" t="s"/>
+      <x:c r="D13" s="16" t="s"/>
+      <x:c r="E13" s="17" t="s"/>
+      <x:c r="F13" s="17" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="s">
-        <x:v>16</x:v>
+      <x:c r="B14" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C14" s="19" t="s"/>
+      <x:c r="D14" s="19" t="s"/>
+      <x:c r="E14" s="19" t="s"/>
+      <x:c r="F14" s="20" t="s">
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="27" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C15" s="28" t="s"/>
-      <x:c r="D15" s="28" t="s"/>
-      <x:c r="E15" s="28" t="s"/>
-      <x:c r="F15" s="29" t="n">
+      <x:c r="B15" s="21" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="s"/>
+      <x:c r="D15" s="22" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="27" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
+      <x:c r="B16" s="21" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C16" s="22" t="s"/>
+      <x:c r="D16" s="22" t="s"/>
+      <x:c r="E16" s="22" t="s"/>
+      <x:c r="F16" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="27" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="28" t="s"/>
-      <x:c r="D17" s="28" t="s"/>
-      <x:c r="E17" s="28" t="s"/>
-      <x:c r="F17" s="29" t="n">
+      <x:c r="B17" s="21" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C17" s="22" t="s"/>
+      <x:c r="D17" s="22" t="s"/>
+      <x:c r="E17" s="22" t="s"/>
+      <x:c r="F17" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C18" s="31" t="s"/>
-      <x:c r="D18" s="31" t="s"/>
-      <x:c r="E18" s="31" t="s"/>
-      <x:c r="F18" s="32" t="n">
+      <x:c r="B18" s="24" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C18" s="25" t="s"/>
+      <x:c r="D18" s="25" t="s"/>
+      <x:c r="E18" s="25" t="s"/>
+      <x:c r="F18" s="26" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -5034,18 +5022,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -5063,166 +5039,178 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46057.234375</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>41712</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1216128</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>630</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>46072.0668055556</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="17" t="s">
+      <x:c r="D7" s="10" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="17" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
-        <x:v>46066.3781828704</x:v>
-      </x:c>
-      <x:c r="I7" s="33">
-        <x:v>46081</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1346991</x:v>
-      </x:c>
-      <x:c r="K7" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>46077.0856712963</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="20" t="s"/>
-      <x:c r="C8" s="20" t="s"/>
-      <x:c r="D8" s="20" t="s"/>
-      <x:c r="E8" s="20" t="s"/>
-      <x:c r="F8" s="20" t="s"/>
-      <x:c r="G8" s="20" t="s"/>
-      <x:c r="H8" s="20" t="s"/>
-      <x:c r="I8" s="20" t="s"/>
-      <x:c r="J8" s="20" t="s"/>
-      <x:c r="K8" s="20" t="s"/>
-      <x:c r="L8" s="20" t="s"/>
-      <x:c r="M8" s="20" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46057.234375</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>41712</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1216128</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46072.0668055556</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="20" t="s"/>
-      <x:c r="C9" s="20" t="s"/>
-      <x:c r="D9" s="20" t="s"/>
-      <x:c r="E9" s="20" t="s"/>
-      <x:c r="F9" s="20" t="s"/>
-      <x:c r="G9" s="20" t="s"/>
-      <x:c r="H9" s="20" t="s"/>
-      <x:c r="I9" s="20" t="s"/>
-      <x:c r="J9" s="20" t="s"/>
-      <x:c r="K9" s="20" t="s"/>
-      <x:c r="L9" s="20" t="s"/>
-      <x:c r="M9" s="20" t="s"/>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46066.3781828704</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>46081</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1346991</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46077.0856712963</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="23" t="s"/>
-      <x:c r="F12" s="23" t="s"/>
+      <x:c r="B12" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C12" s="16" t="s"/>
+      <x:c r="D12" s="16" t="s"/>
+      <x:c r="E12" s="17" t="s"/>
+      <x:c r="F12" s="17" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="s">
-        <x:v>16</x:v>
+      <x:c r="B13" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C13" s="19" t="s"/>
+      <x:c r="D13" s="19" t="s"/>
+      <x:c r="E13" s="19" t="s"/>
+      <x:c r="F13" s="20" t="s">
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="B14" s="21" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="s"/>
+      <x:c r="D14" s="22" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="27" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C15" s="28" t="s"/>
-      <x:c r="D15" s="28" t="s"/>
-      <x:c r="E15" s="28" t="s"/>
-      <x:c r="F15" s="29" t="n">
+      <x:c r="B15" s="21" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="s"/>
+      <x:c r="D15" s="22" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C16" s="31" t="s"/>
-      <x:c r="D16" s="31" t="s"/>
-      <x:c r="E16" s="31" t="s"/>
-      <x:c r="F16" s="32" t="n">
+      <x:c r="B16" s="24" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="s"/>
+      <x:c r="D16" s="25" t="s"/>
+      <x:c r="E16" s="25" t="s"/>
+      <x:c r="F16" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -6325,18 +6313,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -6354,75 +6330,87 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46076.245</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46076.2450115741</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1216190</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>46094.1710416667</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="39" t="s"/>
-      <x:c r="C7" s="39" t="s"/>
-      <x:c r="D7" s="39" t="s"/>
-      <x:c r="E7" s="39" t="s"/>
-      <x:c r="F7" s="39" t="s"/>
-      <x:c r="G7" s="39" t="s"/>
-      <x:c r="H7" s="39" t="s"/>
-      <x:c r="I7" s="39" t="s"/>
-      <x:c r="J7" s="39" t="s"/>
-      <x:c r="K7" s="39" t="s"/>
-      <x:c r="L7" s="39" t="s"/>
-      <x:c r="M7" s="39" t="s"/>
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="20" t="s"/>
-      <x:c r="C8" s="20" t="s"/>
-      <x:c r="D8" s="20" t="s"/>
-      <x:c r="E8" s="20" t="s"/>
-      <x:c r="F8" s="20" t="s"/>
-      <x:c r="G8" s="20" t="s"/>
-      <x:c r="H8" s="20" t="s"/>
-      <x:c r="I8" s="20" t="s"/>
-      <x:c r="J8" s="20" t="s"/>
-      <x:c r="K8" s="20" t="s"/>
-      <x:c r="L8" s="20" t="s"/>
-      <x:c r="M8" s="20" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46076.245</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46076.2450115741</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1216190</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46094.1710416667</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -6440,44 +6428,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="21" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C11" s="22" t="s"/>
-      <x:c r="D11" s="22" t="s"/>
-      <x:c r="E11" s="23" t="s"/>
-      <x:c r="F11" s="23" t="s"/>
+      <x:c r="B11" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="s"/>
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="17" t="s"/>
+      <x:c r="F11" s="17" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="25" t="s"/>
-      <x:c r="D12" s="25" t="s"/>
-      <x:c r="E12" s="25" t="s"/>
-      <x:c r="F12" s="26" t="s">
-        <x:v>16</x:v>
+      <x:c r="B12" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C12" s="19" t="s"/>
+      <x:c r="D12" s="19" t="s"/>
+      <x:c r="E12" s="19" t="s"/>
+      <x:c r="F12" s="20" t="s">
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="27" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C13" s="28" t="s"/>
-      <x:c r="D13" s="28" t="s"/>
-      <x:c r="E13" s="28" t="s"/>
-      <x:c r="F13" s="29" t="n">
+      <x:c r="B13" s="21" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C14" s="31" t="s"/>
-      <x:c r="D14" s="31" t="s"/>
-      <x:c r="E14" s="31" t="s"/>
-      <x:c r="F14" s="32" t="n">
+      <x:c r="B14" s="24" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-DUANE-NICO-CAWALING-evaluator-cache-serviceTracking-DUANE-NICO-CAWALING-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-DUANE-NICO-CAWALING-evaluator-cache-serviceTracking-DUANE-NICO-CAWALING-IX-202501-202612.xlsx
@@ -26,12 +26,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>DUANE NICO CAWALING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IX | July 2025</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -118,6 +121,9 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | August 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>Commercial Radio Operator Certificate (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -163,6 +169,9 @@
     <x:t>61-8-2025-1113</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | November 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
   </x:si>
   <x:si>
@@ -199,6 +208,9 @@
     <x:t>61-10-2025-1215</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | February 2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>EUTIQUIO GERMINA BANAWAN</x:t>
   </x:si>
   <x:si>
@@ -221,6 +233,9 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1330-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IX | March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Retailer/Reseller Permit (NEW)</x:t>
@@ -248,7 +263,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -288,6 +303,30 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -559,12 +598,21 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -579,52 +627,10 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -633,11 +639,53 @@
     <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="14" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="14" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="36">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -668,76 +716,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -756,7 +748,75 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -985,58 +1045,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -1079,171 +1139,171 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="G8" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45860.0993981482</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="16">
         <x:v>45853</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1346409</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>45860.1449537037</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45861.1130439815</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>45861.1130555556</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1346412</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>930</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45862.3035648148</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="s"/>
-      <x:c r="E9" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H9" s="12">
-        <x:v>45861.1130439815</x:v>
-      </x:c>
-      <x:c r="I9" s="12">
-        <x:v>45861.1130555556</x:v>
-      </x:c>
-      <x:c r="J9" s="11" t="n">
-        <x:v>1346412</x:v>
-      </x:c>
-      <x:c r="K9" s="14" t="n">
-        <x:v>930</x:v>
-      </x:c>
-      <x:c r="L9" s="12">
-        <x:v>45862.3035648148</x:v>
-      </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C12" s="16" t="s"/>
-      <x:c r="D12" s="16" t="s"/>
-      <x:c r="E12" s="17" t="s"/>
-      <x:c r="F12" s="17" t="s"/>
+      <x:c r="B12" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C12" s="19" t="s"/>
+      <x:c r="D12" s="19" t="s"/>
+      <x:c r="E12" s="20" t="s"/>
+      <x:c r="F12" s="20" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="18" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C13" s="19" t="s"/>
-      <x:c r="D13" s="19" t="s"/>
-      <x:c r="E13" s="19" t="s"/>
-      <x:c r="F13" s="20" t="s">
+      <x:c r="B13" s="21" t="s">
         <x:v>28</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="21" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="23" t="n">
+      <x:c r="B14" s="24" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="21" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C15" s="22" t="s"/>
-      <x:c r="D15" s="22" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="23" t="n">
+      <x:c r="B15" s="24" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="24" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C16" s="25" t="s"/>
-      <x:c r="D16" s="25" t="s"/>
-      <x:c r="E16" s="25" t="s"/>
-      <x:c r="F16" s="26" t="n">
+      <x:c r="B16" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="28" t="s"/>
+      <x:c r="F16" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -2228,7 +2288,7 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B12:F12"/>
     <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
@@ -2274,58 +2334,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -2368,222 +2428,222 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="F8" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45881.2688541667</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="16">
         <x:v>45927</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1346458</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>45882.0237847222</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="D9" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="E9" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>45870.3069328704</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="16">
         <x:v>46186</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1346441</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="15">
         <x:v>45883.1603356482</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C10" s="27" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D10" s="28" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E10" s="27" t="s">
+      <x:c r="B10" s="30" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F10" s="27" t="s">
+      <x:c r="C10" s="30" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="G10" s="27" t="s">
+      <x:c r="D10" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="H10" s="29">
+      <x:c r="F10" s="30" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H10" s="32">
         <x:v>45881.2806365741</x:v>
       </x:c>
-      <x:c r="I10" s="30">
+      <x:c r="I10" s="33">
         <x:v>45892</x:v>
       </x:c>
-      <x:c r="J10" s="28" t="n">
+      <x:c r="J10" s="31" t="n">
         <x:v>1346470</x:v>
       </x:c>
-      <x:c r="K10" s="31" t="n">
+      <x:c r="K10" s="34" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L10" s="32">
+      <x:c r="L10" s="35">
         <x:v>45883.2976041667</x:v>
       </x:c>
-      <x:c r="M10" s="27" t="s">
-        <x:v>20</x:v>
+      <x:c r="M10" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C13" s="16" t="s"/>
-      <x:c r="D13" s="16" t="s"/>
-      <x:c r="E13" s="17" t="s"/>
-      <x:c r="F13" s="17" t="s"/>
+      <x:c r="B13" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C13" s="19" t="s"/>
+      <x:c r="D13" s="19" t="s"/>
+      <x:c r="E13" s="20" t="s"/>
+      <x:c r="F13" s="20" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="18" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C14" s="19" t="s"/>
-      <x:c r="D14" s="19" t="s"/>
-      <x:c r="E14" s="19" t="s"/>
-      <x:c r="F14" s="20" t="s">
+      <x:c r="B14" s="21" t="s">
         <x:v>28</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="s"/>
+      <x:c r="D14" s="22" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="23" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="21" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C15" s="22" t="s"/>
-      <x:c r="D15" s="22" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="23" t="n">
+      <x:c r="B15" s="24" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="21" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C16" s="22" t="s"/>
-      <x:c r="D16" s="22" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="23" t="n">
+      <x:c r="B16" s="24" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="s"/>
+      <x:c r="D16" s="25" t="s"/>
+      <x:c r="E16" s="25" t="s"/>
+      <x:c r="F16" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="21" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C17" s="22" t="s"/>
-      <x:c r="D17" s="22" t="s"/>
-      <x:c r="E17" s="22" t="s"/>
-      <x:c r="F17" s="23" t="n">
+      <x:c r="B17" s="24" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C17" s="25" t="s"/>
+      <x:c r="D17" s="25" t="s"/>
+      <x:c r="E17" s="25" t="s"/>
+      <x:c r="F17" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="24" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C18" s="25" t="s"/>
-      <x:c r="D18" s="25" t="s"/>
-      <x:c r="E18" s="25" t="s"/>
-      <x:c r="F18" s="26" t="n">
+      <x:c r="B18" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C18" s="28" t="s"/>
+      <x:c r="D18" s="28" t="s"/>
+      <x:c r="E18" s="28" t="s"/>
+      <x:c r="F18" s="29" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -3566,7 +3626,7 @@
   <x:mergeCells count="9">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
     <x:mergeCell ref="B15:E15"/>
@@ -3613,58 +3673,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -3707,220 +3767,220 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s"/>
-      <x:c r="E8" s="11" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45951.1032638889</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="15">
         <x:v>45951.103287037</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1346752</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>45971.0888194444</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="B9" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>45980.2160416667</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="16">
         <x:v>45979</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1346786</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>5280</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="15">
         <x:v>45985.3594791667</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C10" s="27" t="s">
+      <x:c r="B10" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D10" s="28" t="s">
+      <x:c r="C10" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="27" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F10" s="27" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G10" s="27" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H10" s="29">
+      <x:c r="D10" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F10" s="30" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H10" s="32">
         <x:v>45959.0699074074</x:v>
       </x:c>
-      <x:c r="I10" s="30">
+      <x:c r="I10" s="33">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J10" s="28" t="n">
+      <x:c r="J10" s="31" t="n">
         <x:v>1346761</x:v>
       </x:c>
-      <x:c r="K10" s="31" t="n">
+      <x:c r="K10" s="34" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="32">
+      <x:c r="L10" s="35">
         <x:v>45972.2719560185</x:v>
       </x:c>
-      <x:c r="M10" s="27" t="s">
-        <x:v>20</x:v>
+      <x:c r="M10" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C13" s="16" t="s"/>
-      <x:c r="D13" s="16" t="s"/>
-      <x:c r="E13" s="17" t="s"/>
-      <x:c r="F13" s="17" t="s"/>
+      <x:c r="B13" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C13" s="19" t="s"/>
+      <x:c r="D13" s="19" t="s"/>
+      <x:c r="E13" s="20" t="s"/>
+      <x:c r="F13" s="20" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="18" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C14" s="19" t="s"/>
-      <x:c r="D14" s="19" t="s"/>
-      <x:c r="E14" s="19" t="s"/>
-      <x:c r="F14" s="20" t="s">
+      <x:c r="B14" s="21" t="s">
         <x:v>28</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="s"/>
+      <x:c r="D14" s="22" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="23" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="21" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C15" s="22" t="s"/>
-      <x:c r="D15" s="22" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="23" t="n">
+      <x:c r="B15" s="24" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="21" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C16" s="22" t="s"/>
-      <x:c r="D16" s="22" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="23" t="n">
+      <x:c r="B16" s="24" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="s"/>
+      <x:c r="D16" s="25" t="s"/>
+      <x:c r="E16" s="25" t="s"/>
+      <x:c r="F16" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="21" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C17" s="22" t="s"/>
-      <x:c r="D17" s="22" t="s"/>
-      <x:c r="E17" s="22" t="s"/>
-      <x:c r="F17" s="23" t="n">
+      <x:c r="B17" s="24" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C17" s="25" t="s"/>
+      <x:c r="D17" s="25" t="s"/>
+      <x:c r="E17" s="25" t="s"/>
+      <x:c r="F17" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="24" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C18" s="25" t="s"/>
-      <x:c r="D18" s="25" t="s"/>
-      <x:c r="E18" s="25" t="s"/>
-      <x:c r="F18" s="26" t="n">
+      <x:c r="B18" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C18" s="28" t="s"/>
+      <x:c r="D18" s="28" t="s"/>
+      <x:c r="E18" s="28" t="s"/>
+      <x:c r="F18" s="29" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -4903,7 +4963,7 @@
   <x:mergeCells count="9">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
     <x:mergeCell ref="B15:E15"/>
@@ -4950,58 +5010,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -5044,173 +5104,173 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G8" s="11" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="B8" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46057.234375</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="16">
         <x:v>41712</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1216128</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>630</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>46072.0668055556</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>61</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="B9" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>46066.3781828704</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="16">
         <x:v>46081</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1346991</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="15">
         <x:v>46077.0856712963</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C12" s="16" t="s"/>
-      <x:c r="D12" s="16" t="s"/>
-      <x:c r="E12" s="17" t="s"/>
-      <x:c r="F12" s="17" t="s"/>
+      <x:c r="B12" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C12" s="19" t="s"/>
+      <x:c r="D12" s="19" t="s"/>
+      <x:c r="E12" s="20" t="s"/>
+      <x:c r="F12" s="20" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="18" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C13" s="19" t="s"/>
-      <x:c r="D13" s="19" t="s"/>
-      <x:c r="E13" s="19" t="s"/>
-      <x:c r="F13" s="20" t="s">
+      <x:c r="B13" s="21" t="s">
         <x:v>28</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="21" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="23" t="n">
+      <x:c r="B14" s="24" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="21" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C15" s="22" t="s"/>
-      <x:c r="D15" s="22" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="23" t="n">
+      <x:c r="B15" s="24" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="24" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C16" s="25" t="s"/>
-      <x:c r="D16" s="25" t="s"/>
-      <x:c r="E16" s="25" t="s"/>
-      <x:c r="F16" s="26" t="n">
+      <x:c r="B16" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="28" t="s"/>
+      <x:c r="F16" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -6195,7 +6255,7 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B12:F12"/>
     <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
@@ -6241,58 +6301,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -6335,81 +6395,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>46076.245</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46076.2450115741</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1216190</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46094.1710416667</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="G8" s="11" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="H8" s="12">
-        <x:v>46076.245</x:v>
-      </x:c>
-      <x:c r="I8" s="12">
-        <x:v>46076.2450115741</x:v>
-      </x:c>
-      <x:c r="J8" s="11" t="n">
-        <x:v>1216190</x:v>
-      </x:c>
-      <x:c r="K8" s="14" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L8" s="12">
-        <x:v>46094.1710416667</x:v>
-      </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -6428,44 +6488,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s"/>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="17" t="s"/>
-      <x:c r="F11" s="17" t="s"/>
+      <x:c r="B11" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="18" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="s"/>
-      <x:c r="D12" s="19" t="s"/>
-      <x:c r="E12" s="19" t="s"/>
-      <x:c r="F12" s="20" t="s">
+      <x:c r="B12" s="21" t="s">
         <x:v>28</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="n">
+      <x:c r="B13" s="24" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
+      <x:c r="B14" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -7452,7 +7512,7 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
     <x:mergeCell ref="B13:E13"/>

--- a/reports/service-tracking-report-DUANE-NICO-CAWALING-evaluator-cache-serviceTracking-DUANE-NICO-CAWALING-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-DUANE-NICO-CAWALING-evaluator-cache-serviceTracking-DUANE-NICO-CAWALING-IX-202501-202612.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -71,42 +71,6 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ApplicationType}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Name}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Status}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Address}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.PermitNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ReferenceNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DateOfFiling}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ExpirationDate}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Amount}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DatePaid}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
@@ -301,7 +265,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -345,14 +309,6 @@
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
-      <x:sz val="16"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
@@ -367,10 +323,18 @@
       <x:family val="2"/>
     </x:font>
     <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -385,6 +349,13 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -621,7 +592,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="27">
+  <x:cellStyleXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -629,16 +600,16 @@
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -650,13 +621,7 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -686,10 +651,13 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -701,8 +669,17 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -733,28 +710,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -767,10 +736,6 @@
     </x:xf>
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -797,15 +762,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -819,6 +784,26 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -1150,7 +1135,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1190,188 +1175,138 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="9" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="H8" s="15">
+        <x:v>45860.0993981482</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>45853</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1346409</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45860.1449537037</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="M8" s="9" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45861.1130439815</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>45861.1130555556</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1346412</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>930</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45862.3035648148</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="17" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="s"/>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="19" t="s"/>
+      <x:c r="F12" s="19" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="20" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45860.0993981482</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>45853</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1346409</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>45860.1449537037</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>45861.1130439815</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>45861.1130555556</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1346412</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>930</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>45862.3035648148</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>33</x:v>
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="20" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="22" t="s"/>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
       <x:c r="B15" s="23" t="s">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C15" s="24" t="s"/>
       <x:c r="D15" s="24" t="s"/>
       <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="s">
-        <x:v>41</x:v>
+      <x:c r="F15" s="25" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
       <x:c r="B16" s="26" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C16" s="27" t="s"/>
       <x:c r="D16" s="27" t="s"/>
       <x:c r="E16" s="27" t="s"/>
       <x:c r="F16" s="28" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="29" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C18" s="30" t="s"/>
-      <x:c r="D18" s="30" t="s"/>
-      <x:c r="E18" s="30" t="s"/>
-      <x:c r="F18" s="31" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2353,11 +2288,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B14:F14"/>
+    <x:mergeCell ref="B12:F12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
-    <x:mergeCell ref="B17:E17"/>
-    <x:mergeCell ref="B18:E18"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -2469,7 +2404,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -2502,7 +2437,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -2542,239 +2477,189 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="9" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="E8" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>45881.2688541667</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>45927</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1346458</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45882.0237847222</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J8" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="K8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L8" s="9" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45870.3069328704</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>46186</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1346441</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45883.1603356482</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="29" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D10" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="29" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="F10" s="29" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="G10" s="29" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H10" s="31">
+        <x:v>45881.2806365741</x:v>
+      </x:c>
+      <x:c r="I10" s="31">
+        <x:v>45892</x:v>
+      </x:c>
+      <x:c r="J10" s="30" t="n">
+        <x:v>1346470</x:v>
+      </x:c>
+      <x:c r="K10" s="32" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L10" s="33">
+        <x:v>45883.2976041667</x:v>
+      </x:c>
+      <x:c r="M10" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="17" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="s"/>
+      <x:c r="D13" s="18" t="s"/>
+      <x:c r="E13" s="19" t="s"/>
+      <x:c r="F13" s="19" t="s"/>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="20" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45881.2688541667</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>45927</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1346458</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>45882.0237847222</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="23" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="23" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>45870.3069328704</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>46186</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1346441</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>45883.1603356482</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>45881.2806365741</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>45892</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1346470</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L12" s="19">
-        <x:v>45883.2976041667</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="20" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C15" s="21" t="s"/>
-      <x:c r="D15" s="21" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="22" t="s"/>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="23" t="s">
-        <x:v>40</x:v>
       </x:c>
       <x:c r="C16" s="24" t="s"/>
       <x:c r="D16" s="24" t="s"/>
       <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="25" t="s">
-        <x:v>41</x:v>
+      <x:c r="F16" s="25" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="B17" s="23" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C17" s="24" t="s"/>
+      <x:c r="D17" s="24" t="s"/>
+      <x:c r="E17" s="24" t="s"/>
+      <x:c r="F17" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+    <x:row r="18" spans="1:28" ht="28" customHeight="1">
       <x:c r="B18" s="26" t="s">
-        <x:v>49</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C18" s="27" t="s"/>
       <x:c r="D18" s="27" t="s"/>
       <x:c r="E18" s="27" t="s"/>
       <x:c r="F18" s="28" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="29" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C20" s="30" t="s"/>
-      <x:c r="D20" s="30" t="s"/>
-      <x:c r="E20" s="30" t="s"/>
-      <x:c r="F20" s="31" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3754,12 +3639,12 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B15:F15"/>
+    <x:mergeCell ref="B13:F13"/>
+    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
-    <x:mergeCell ref="B19:E19"/>
-    <x:mergeCell ref="B20:E20"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -3871,7 +3756,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -3904,7 +3789,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -3944,237 +3829,187 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>45951.1032638889</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>45951.103287037</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1346752</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45971.0888194444</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D9" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="E9" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45980.2160416667</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>45979</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1346786</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>5280</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45985.3594791667</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J8" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="K8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45951.1032638889</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>45951.103287037</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1346752</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>45971.0888194444</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>33</x:v>
+      <x:c r="B10" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D10" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="29" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F10" s="29" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G10" s="29" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H10" s="31">
+        <x:v>45959.0699074074</x:v>
+      </x:c>
+      <x:c r="I10" s="31">
+        <x:v>45964</x:v>
+      </x:c>
+      <x:c r="J10" s="30" t="n">
+        <x:v>1346761</x:v>
+      </x:c>
+      <x:c r="K10" s="32" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="33">
+        <x:v>45972.2719560185</x:v>
+      </x:c>
+      <x:c r="M10" s="29" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="17" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="s"/>
+      <x:c r="D13" s="18" t="s"/>
+      <x:c r="E13" s="19" t="s"/>
+      <x:c r="F13" s="19" t="s"/>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="20" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>45980.2160416667</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>45979</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1346786</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>5280</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>45985.3594791667</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>45959.0699074074</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>45964</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1346761</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L12" s="19">
-        <x:v>45972.2719560185</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>33</x:v>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="23" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="20" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C15" s="21" t="s"/>
-      <x:c r="D15" s="21" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="22" t="s"/>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="22" customHeight="1">
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
       <x:c r="B16" s="23" t="s">
-        <x:v>40</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C16" s="24" t="s"/>
       <x:c r="D16" s="24" t="s"/>
       <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="25" t="s">
-        <x:v>41</x:v>
+      <x:c r="F16" s="25" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="B17" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C17" s="24" t="s"/>
+      <x:c r="D17" s="24" t="s"/>
+      <x:c r="E17" s="24" t="s"/>
+      <x:c r="F17" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+    <x:row r="18" spans="1:28" ht="28" customHeight="1">
       <x:c r="B18" s="26" t="s">
-        <x:v>65</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C18" s="27" t="s"/>
       <x:c r="D18" s="27" t="s"/>
       <x:c r="E18" s="27" t="s"/>
       <x:c r="F18" s="28" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="29" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C20" s="30" t="s"/>
-      <x:c r="D20" s="30" t="s"/>
-      <x:c r="E20" s="30" t="s"/>
-      <x:c r="F20" s="31" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5154,12 +4989,12 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B15:F15"/>
+    <x:mergeCell ref="B13:F13"/>
+    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
-    <x:mergeCell ref="B19:E19"/>
-    <x:mergeCell ref="B20:E20"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -5271,7 +5106,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -5304,7 +5139,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -5344,190 +5179,140 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>46057.234375</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>41712</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1216128</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46072.0668055556</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D9" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="E9" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>46066.3781828704</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>46081</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1346991</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46077.0856712963</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J8" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="K8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="17" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="s"/>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="19" t="s"/>
+      <x:c r="F12" s="19" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="20" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46057.234375</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>41712</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1216128</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>630</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46072.0668055556</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>77</x:v>
-      </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>46066.3781828704</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>46081</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1346991</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>46077.0856712963</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>33</x:v>
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="23" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="20" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="22" t="s"/>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
       <x:c r="B15" s="23" t="s">
-        <x:v>40</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C15" s="24" t="s"/>
       <x:c r="D15" s="24" t="s"/>
       <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="s">
-        <x:v>41</x:v>
+      <x:c r="F15" s="25" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
       <x:c r="B16" s="26" t="s">
-        <x:v>44</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C16" s="27" t="s"/>
       <x:c r="D16" s="27" t="s"/>
       <x:c r="E16" s="27" t="s"/>
       <x:c r="F16" s="28" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="29" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C18" s="30" t="s"/>
-      <x:c r="D18" s="30" t="s"/>
-      <x:c r="E18" s="30" t="s"/>
-      <x:c r="F18" s="31" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6509,11 +6294,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B14:F14"/>
+    <x:mergeCell ref="B12:F12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
-    <x:mergeCell ref="B17:E17"/>
-    <x:mergeCell ref="B18:E18"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -6625,7 +6410,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>81</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -6658,7 +6443,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -6698,141 +6483,104 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="9" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="I8" s="9" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J8" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="K8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
+      <x:c r="B8" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>46076.245</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46076.2450115741</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1216190</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46094.1710416667</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>65</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46076.245</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46076.2450115741</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1216190</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46094.1710416667</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>77</x:v>
-      </x:c>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="17" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="20" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
+        <x:v>29</x:v>
+      </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
-        <x:v>41</x:v>
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="23" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="26" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7816,10 +7564,10 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B13:F13"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DUANE-NICO-CAWALING-evaluator-cache-serviceTracking-DUANE-NICO-CAWALING-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-DUANE-NICO-CAWALING-evaluator-cache-serviceTracking-DUANE-NICO-CAWALING-IX-202501-202612.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -91,6 +91,9 @@
     <x:t>61-7-2025-1070</x:t>
   </x:si>
   <x:si>
+    <x:t>1346409</x:t>
+  </x:si>
+  <x:si>
     <x:t>Neil Jon Angeles</x:t>
   </x:si>
   <x:si>
@@ -109,6 +112,9 @@
     <x:t>61-7-2025-1072</x:t>
   </x:si>
   <x:si>
+    <x:t>1346412</x:t>
+  </x:si>
+  <x:si>
     <x:t>SUMMARY</x:t>
   </x:si>
   <x:si>
@@ -139,6 +145,9 @@
     <x:t>61-8-2025-1112</x:t>
   </x:si>
   <x:si>
+    <x:t>1346458</x:t>
+  </x:si>
+  <x:si>
     <x:t>Ship Station License DOMESTIC Trade (MODIFICATION)</x:t>
   </x:si>
   <x:si>
@@ -154,6 +163,9 @@
     <x:t>61-8-2025-1087</x:t>
   </x:si>
   <x:si>
+    <x:t>1346441</x:t>
+  </x:si>
+  <x:si>
     <x:t>Ship Station License DOMESTIC Trade (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -169,6 +181,9 @@
     <x:t>61-8-2025-1113</x:t>
   </x:si>
   <x:si>
+    <x:t>1346470</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | November 2025</x:t>
   </x:si>
   <x:si>
@@ -187,6 +202,9 @@
     <x:t>61-10-2025-1198</x:t>
   </x:si>
   <x:si>
+    <x:t>1346752</x:t>
+  </x:si>
+  <x:si>
     <x:t>Dealer Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -199,6 +217,9 @@
     <x:t>61-11-2025-1245-086</x:t>
   </x:si>
   <x:si>
+    <x:t>1346786</x:t>
+  </x:si>
+  <x:si>
     <x:t>Makuguihon, Molave, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -208,6 +229,9 @@
     <x:t>61-10-2025-1215</x:t>
   </x:si>
   <x:si>
+    <x:t>1346761</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | February 2026</x:t>
   </x:si>
   <x:si>
@@ -223,6 +247,9 @@
     <x:t>61-2-2026-1309-810</x:t>
   </x:si>
   <x:si>
+    <x:t>1216128</x:t>
+  </x:si>
+  <x:si>
     <x:t>Catalina EBON</x:t>
   </x:si>
   <x:si>
@@ -235,6 +262,9 @@
     <x:t>61-2-2026-1330-585</x:t>
   </x:si>
   <x:si>
+    <x:t>1346991</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | March 2026</x:t>
   </x:si>
   <x:si>
@@ -254,6 +284,9 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1355-880</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216190</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -334,7 +367,7 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -357,7 +390,7 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
   </x:fonts>
@@ -651,13 +684,10 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -667,6 +697,9 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -727,6 +760,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -736,6 +773,10 @@
     </x:xf>
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -762,15 +803,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -787,10 +828,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -800,10 +837,6 @@
     </x:xf>
     <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -1183,7 +1216,7 @@
       <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
@@ -1195,113 +1228,113 @@
       <x:c r="G8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45860.0993981482</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="H8" s="16">
+        <x:v>45860.0994011343</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
         <x:v>45853</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1346409</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45860.1449537037</x:v>
+      <x:c r="L8" s="18">
+        <x:v>45860.1449620718</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s"/>
+      <x:c r="E9" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>45861.1130539236</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>45861.113062963</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>930</x:v>
+      </x:c>
+      <x:c r="L9" s="18">
+        <x:v>45862.3035735301</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45861.1130439815</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>45861.1130555556</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1346412</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
-        <x:v>930</x:v>
-      </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45862.3035648148</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C12" s="18" t="s"/>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="19" t="s"/>
-      <x:c r="F12" s="19" t="s"/>
+      <x:c r="B12" s="19" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C12" s="20" t="s"/>
+      <x:c r="D12" s="20" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="21" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="22" t="s">
-        <x:v>29</x:v>
+      <x:c r="B13" s="22" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C13" s="23" t="s"/>
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="23" t="s"/>
+      <x:c r="F13" s="24" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="23" t="s">
+      <x:c r="B14" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="n">
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="23" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="n">
+      <x:c r="B15" s="25" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="26" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="B16" s="28" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -2404,7 +2437,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -2480,181 +2513,181 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45881.2688541667</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>45881.2688653125</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
         <x:v>45927</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1346458</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45882.0237847222</x:v>
+      <x:c r="L8" s="18">
+        <x:v>45882.0237933565</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45870.3069328704</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>45870.3069341667</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
         <x:v>46186</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1346441</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="15" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45883.1603356482</x:v>
+      <x:c r="L9" s="18">
+        <x:v>45883.1603418287</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="29" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C10" s="29" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D10" s="30" t="s">
+      <x:c r="B10" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E10" s="29" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F10" s="29" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G10" s="29" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H10" s="31">
-        <x:v>45881.2806365741</x:v>
-      </x:c>
-      <x:c r="I10" s="31">
+      <x:c r="E10" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>45881.2806375231</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
         <x:v>45892</x:v>
       </x:c>
-      <x:c r="J10" s="30" t="n">
-        <x:v>1346470</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
+      <x:c r="J10" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L10" s="33">
-        <x:v>45883.2976041667</x:v>
-      </x:c>
-      <x:c r="M10" s="29" t="s">
-        <x:v>21</x:v>
+      <x:c r="L10" s="18">
+        <x:v>45883.297613287</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C13" s="18" t="s"/>
-      <x:c r="D13" s="18" t="s"/>
-      <x:c r="E13" s="19" t="s"/>
-      <x:c r="F13" s="19" t="s"/>
+      <x:c r="B13" s="19" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C13" s="20" t="s"/>
+      <x:c r="D13" s="20" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="21" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="20" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="22" t="s">
-        <x:v>29</x:v>
+      <x:c r="B14" s="22" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="24" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="23" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="n">
+      <x:c r="B15" s="25" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="23" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C16" s="24" t="s"/>
-      <x:c r="D16" s="24" t="s"/>
-      <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="25" t="n">
+      <x:c r="B16" s="25" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="23" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C17" s="24" t="s"/>
-      <x:c r="D17" s="24" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="25" t="n">
+      <x:c r="B17" s="25" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="26" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
+      <x:c r="B18" s="28" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -3756,7 +3789,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -3832,179 +3865,179 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s"/>
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s"/>
       <x:c r="E8" s="14" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45951.1032638889</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>45951.103287037</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1346752</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>45951.1032693866</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>45951.1032970718</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45971.0888194444</x:v>
+      <x:c r="L8" s="18">
+        <x:v>45971.088825787</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45980.2160416667</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>45980.216052338</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
         <x:v>45979</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1346786</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="15" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>5280</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45985.3594791667</x:v>
+      <x:c r="L9" s="18">
+        <x:v>45985.3594797917</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="29" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="29" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D10" s="30" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E10" s="29" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F10" s="29" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G10" s="29" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H10" s="31">
-        <x:v>45959.0699074074</x:v>
-      </x:c>
-      <x:c r="I10" s="31">
+      <x:c r="E10" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>45959.0699130787</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J10" s="30" t="n">
-        <x:v>1346761</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
+      <x:c r="J10" s="15" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="33">
-        <x:v>45972.2719560185</x:v>
-      </x:c>
-      <x:c r="M10" s="29" t="s">
-        <x:v>21</x:v>
+      <x:c r="L10" s="18">
+        <x:v>45972.2719636111</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C13" s="18" t="s"/>
-      <x:c r="D13" s="18" t="s"/>
-      <x:c r="E13" s="19" t="s"/>
-      <x:c r="F13" s="19" t="s"/>
+      <x:c r="B13" s="19" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C13" s="20" t="s"/>
+      <x:c r="D13" s="20" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="21" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="20" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="22" t="s">
-        <x:v>29</x:v>
+      <x:c r="B14" s="22" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="24" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="23" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="n">
+      <x:c r="B15" s="25" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="23" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C16" s="24" t="s"/>
-      <x:c r="D16" s="24" t="s"/>
-      <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="25" t="n">
+      <x:c r="B16" s="25" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="23" t="s">
+      <x:c r="B17" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C17" s="24" t="s"/>
-      <x:c r="D17" s="24" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="25" t="n">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="26" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
+      <x:c r="B18" s="28" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -5106,7 +5139,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -5182,132 +5215,132 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>62</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>63</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46057.234375</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46057.2343839583</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
         <x:v>41712</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1216128</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="15" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>630</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46072.0668055556</x:v>
+      <x:c r="L8" s="18">
+        <x:v>46072.0668155208</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>65</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>66</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>67</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46066.3781828704</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46066.3781940972</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
         <x:v>46081</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1346991</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="15" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46077.0856712963</x:v>
+      <x:c r="L9" s="18">
+        <x:v>46077.0856746296</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C12" s="18" t="s"/>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="19" t="s"/>
-      <x:c r="F12" s="19" t="s"/>
+      <x:c r="B12" s="19" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C12" s="20" t="s"/>
+      <x:c r="D12" s="20" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="21" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="22" t="s">
-        <x:v>29</x:v>
+      <x:c r="B13" s="22" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C13" s="23" t="s"/>
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="23" t="s"/>
+      <x:c r="F13" s="24" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="n">
+      <x:c r="B14" s="25" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="23" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="n">
+      <x:c r="B15" s="25" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="26" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="B16" s="28" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -6410,7 +6443,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -6485,41 +6518,41 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="B8" s="31" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C8" s="31" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D8" s="31" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="E8" s="31" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="F8" s="31" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G8" s="31" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H8" s="32">
+        <x:v>46076.2450058565</x:v>
+      </x:c>
+      <x:c r="I8" s="32">
+        <x:v>46076.2450229514</x:v>
+      </x:c>
+      <x:c r="J8" s="31" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="K8" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L8" s="32">
+        <x:v>46094.1710418981</x:v>
+      </x:c>
+      <x:c r="M8" s="31" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46076.245</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>46076.2450115741</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1216190</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46094.1710416667</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -6538,44 +6571,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+      <x:c r="B11" s="19" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C11" s="20" t="s"/>
+      <x:c r="D11" s="20" t="s"/>
+      <x:c r="E11" s="21" t="s"/>
+      <x:c r="F11" s="21" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
-        <x:v>29</x:v>
+      <x:c r="B12" s="22" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C12" s="23" t="s"/>
+      <x:c r="D12" s="23" t="s"/>
+      <x:c r="E12" s="23" t="s"/>
+      <x:c r="F12" s="24" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+      <x:c r="B13" s="25" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C13" s="26" t="s"/>
+      <x:c r="D13" s="26" t="s"/>
+      <x:c r="E13" s="26" t="s"/>
+      <x:c r="F13" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="B14" s="28" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C14" s="29" t="s"/>
+      <x:c r="D14" s="29" t="s"/>
+      <x:c r="E14" s="29" t="s"/>
+      <x:c r="F14" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-DUANE-NICO-CAWALING-evaluator-cache-serviceTracking-DUANE-NICO-CAWALING-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-DUANE-NICO-CAWALING-evaluator-cache-serviceTracking-DUANE-NICO-CAWALING-IX-202501-202612.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -287,6 +287,42 @@
   </x:si>
   <x:si>
     <x:t>1216190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ayala, Zamboanga City, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-II0629F-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1399-659</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1347138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sangali, Zamboanga City, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-II0630F-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1398-278</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1347137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VETERANS VILLAGE, Ipil (Capital), Zamboanga Sibugay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-II0601G-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1397-805</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1347135</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -298,7 +334,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -384,13 +420,6 @@
       <x:sz val="14"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
   </x:fonts>
@@ -625,7 +654,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="29">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -699,20 +728,8 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -825,18 +842,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -6518,104 +6523,212 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="31" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C8" s="31" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="D8" s="31" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="E8" s="31" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="F8" s="31" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="G8" s="31" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="H8" s="32">
+      <x:c r="H8" s="16">
         <x:v>46076.2450058565</x:v>
       </x:c>
-      <x:c r="I8" s="32">
+      <x:c r="I8" s="16">
         <x:v>46076.2450229514</x:v>
       </x:c>
-      <x:c r="J8" s="31" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="K8" s="33" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L8" s="32">
+      <x:c r="L8" s="18">
         <x:v>46094.1710418981</x:v>
       </x:c>
-      <x:c r="M8" s="31" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>74</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46094.3289943287</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L9" s="18">
+        <x:v>46107.1436918634</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="19" t="s">
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46094.3273162269</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="18">
+        <x:v>46107.1513918519</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46094.3172049306</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="18">
+        <x:v>46107.1610127431</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="19" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C11" s="20" t="s"/>
-      <x:c r="D11" s="20" t="s"/>
-      <x:c r="E11" s="21" t="s"/>
-      <x:c r="F11" s="21" t="s"/>
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="21" t="s"/>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="22" t="s">
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="22" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C12" s="23" t="s"/>
-      <x:c r="D12" s="23" t="s"/>
-      <x:c r="E12" s="23" t="s"/>
-      <x:c r="F12" s="24" t="s">
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="s">
         <x:v>31</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="25" t="s">
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="25" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C13" s="26" t="s"/>
-      <x:c r="D13" s="26" t="s"/>
-      <x:c r="E13" s="26" t="s"/>
-      <x:c r="F13" s="27" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="28" t="s">
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="25" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B18" s="28" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C14" s="29" t="s"/>
-      <x:c r="D14" s="29" t="s"/>
-      <x:c r="E14" s="29" t="s"/>
-      <x:c r="F14" s="30" t="n">
-        <x:v>1</x:v>
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7592,15 +7705,16 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
+  <x:mergeCells count="9">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
-    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B14:F14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DUANE-NICO-CAWALING-evaluator-cache-serviceTracking-DUANE-NICO-CAWALING-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-DUANE-NICO-CAWALING-evaluator-cache-serviceTracking-DUANE-NICO-CAWALING-IX-202501-202612.xlsx
@@ -1173,7 +1173,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1213,7 +1213,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -1252,7 +1252,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -2475,7 +2475,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -2515,7 +2515,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>34</x:v>
@@ -2554,7 +2554,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>40</x:v>
       </x:c>
@@ -2592,7 +2592,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>46</x:v>
       </x:c>
@@ -3827,7 +3827,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -3867,7 +3867,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>53</x:v>
@@ -3904,7 +3904,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
@@ -3942,7 +3942,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -5177,7 +5177,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -5217,7 +5217,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>34</x:v>
@@ -5256,7 +5256,7 @@
         <x:v>74</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
@@ -6481,7 +6481,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -6521,7 +6521,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>80</x:v>
@@ -6560,7 +6560,7 @@
         <x:v>74</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -6598,7 +6598,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -6636,7 +6636,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>

--- a/reports/service-tracking-report-DUANE-NICO-CAWALING-evaluator-cache-serviceTracking-DUANE-NICO-CAWALING-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-DUANE-NICO-CAWALING-evaluator-cache-serviceTracking-DUANE-NICO-CAWALING-IX-202501-202612.xlsx
@@ -28,7 +28,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
   <x:si>
-    <x:t>EVALUATOR SUMMARY</x:t>
+    <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
   <x:si>
     <x:t>DUANE NICO CAWALING</x:t>

--- a/reports/service-tracking-report-DUANE-NICO-CAWALING-evaluator-cache-serviceTracking-DUANE-NICO-CAWALING-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-DUANE-NICO-CAWALING-evaluator-cache-serviceTracking-DUANE-NICO-CAWALING-IX-202501-202612.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -34,9 +34,6 @@
     <x:t>DUANE NICO CAWALING</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | July 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>Application Type</x:t>
   </x:si>
   <x:si>
@@ -127,9 +124,6 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | August 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>Commercial Radio Operator Certificate (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -184,9 +178,6 @@
     <x:t>1346470</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | November 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
   </x:si>
   <x:si>
@@ -232,9 +223,6 @@
     <x:t>1346761</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | February 2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>EUTIQUIO GERMINA BANAWAN</x:t>
   </x:si>
   <x:si>
@@ -263,9 +251,6 @@
   </x:si>
   <x:si>
     <x:t>1346991</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IX | March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Retailer/Reseller Permit (NEW)</x:t>
@@ -654,7 +639,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -669,6 +654,9 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -729,7 +717,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -765,6 +753,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1139,20 +1131,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45839</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1175,171 +1167,171 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="D8" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
+      <x:c r="E8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="H8" s="17">
+        <x:v>45860.0994011343</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>45853</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>45860.0994011343</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>45853</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="K8" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>45860.1449620718</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>45860.1449620718</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
+      <x:c r="B9" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="D9" s="16" t="s"/>
+      <x:c r="E9" s="15" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="F9" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="H9" s="17">
+        <x:v>45861.1130539236</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>45861.113062963</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>45861.1130539236</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>45861.113062963</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="K9" s="18" t="n">
         <x:v>930</x:v>
       </x:c>
-      <x:c r="L9" s="18">
+      <x:c r="L9" s="19">
         <x:v>45862.3035735301</x:v>
       </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="19" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C12" s="20" t="s"/>
-      <x:c r="D12" s="20" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="21" t="s"/>
+      <x:c r="B12" s="20" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="22" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="22" t="s">
+      <x:c r="B13" s="23" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="C13" s="23" t="s"/>
-      <x:c r="D13" s="23" t="s"/>
-      <x:c r="E13" s="23" t="s"/>
-      <x:c r="F13" s="24" t="s">
-        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C14" s="26" t="s"/>
-      <x:c r="D14" s="26" t="s"/>
-      <x:c r="E14" s="26" t="s"/>
-      <x:c r="F14" s="27" t="n">
+      <x:c r="B14" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="n">
+      <x:c r="B15" s="26" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="28" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="30" t="n">
+      <x:c r="B16" s="29" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -2441,20 +2433,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45870</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2477,222 +2469,222 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="H8" s="17">
+        <x:v>45881.2688653125</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>45927</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H8" s="16">
-        <x:v>45881.2688653125</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>45927</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K8" s="18" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L8" s="18">
+      <x:c r="L8" s="19">
         <x:v>45882.0237933565</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M8" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
+      <x:c r="B9" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="E9" s="15" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s">
+      <x:c r="F9" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="H9" s="17">
+        <x:v>45870.3069341667</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46186</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
-        <x:v>45870.3069341667</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46186</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="K9" s="18" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L9" s="18">
+      <x:c r="L9" s="19">
         <x:v>45883.1603418287</x:v>
       </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
+      <x:c r="B10" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="H10" s="17">
+        <x:v>45881.2806375231</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45892</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45881.2806375231</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>45892</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L10" s="19">
         <x:v>45883.297613287</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M10" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="19" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C13" s="20" t="s"/>
-      <x:c r="D13" s="20" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="21" t="s"/>
+      <x:c r="B13" s="20" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="22" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="22" t="s">
+      <x:c r="B14" s="23" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="24" t="s">
-        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="n">
+      <x:c r="B15" s="26" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="n">
+      <x:c r="B16" s="26" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="n">
+      <x:c r="B17" s="26" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="28" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C18" s="29" t="s"/>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="29" t="s"/>
-      <x:c r="F18" s="30" t="n">
+      <x:c r="B18" s="29" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C18" s="30" t="s"/>
+      <x:c r="D18" s="30" t="s"/>
+      <x:c r="E18" s="30" t="s"/>
+      <x:c r="F18" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -3793,20 +3785,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45962</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3829,220 +3821,220 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s"/>
+      <x:c r="E8" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="H8" s="17">
+        <x:v>45951.1032693866</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>45951.1032970718</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="H8" s="16">
-        <x:v>45951.1032693866</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>45951.1032970718</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K8" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="18">
+      <x:c r="L8" s="19">
         <x:v>45971.088825787</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M8" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
+      <x:c r="B9" s="15" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="H9" s="17">
+        <x:v>45980.216052338</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>45979</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
-        <x:v>45980.216052338</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>45979</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="K9" s="18" t="n">
         <x:v>5280</x:v>
       </x:c>
-      <x:c r="L9" s="18">
+      <x:c r="L9" s="19">
         <x:v>45985.3594797917</x:v>
       </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="D10" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="E10" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>45959.0699130787</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45964</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45959.0699130787</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>45964</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L10" s="19">
         <x:v>45972.2719636111</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M10" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="19" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C13" s="20" t="s"/>
-      <x:c r="D13" s="20" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="21" t="s"/>
+      <x:c r="B13" s="20" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="22" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="22" t="s">
+      <x:c r="B14" s="23" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="24" t="s">
-        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="n">
+      <x:c r="B15" s="26" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="n">
+      <x:c r="B16" s="26" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="n">
+      <x:c r="B17" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="28" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C18" s="29" t="s"/>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="29" t="s"/>
-      <x:c r="F18" s="30" t="n">
+      <x:c r="B18" s="29" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C18" s="30" t="s"/>
+      <x:c r="D18" s="30" t="s"/>
+      <x:c r="E18" s="30" t="s"/>
+      <x:c r="F18" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -5143,20 +5135,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46054</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -5179,173 +5171,173 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H8" s="17">
+        <x:v>46057.2343839583</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>41712</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="K8" s="18" t="n">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46072.0668155208</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
         <x:v>70</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46057.2343839583</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>41712</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>630</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46072.0668155208</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="B9" s="15" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
+      <x:c r="E9" s="15" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H9" s="17">
         <x:v>46066.3781940972</x:v>
       </x:c>
-      <x:c r="I9" s="16">
+      <x:c r="I9" s="17">
         <x:v>46081</x:v>
       </x:c>
-      <x:c r="J9" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="J9" s="16" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="K9" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="18">
+      <x:c r="L9" s="19">
         <x:v>46077.0856746296</x:v>
       </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="19" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C12" s="20" t="s"/>
-      <x:c r="D12" s="20" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="21" t="s"/>
+      <x:c r="B12" s="20" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="22" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="22" t="s">
+      <x:c r="B13" s="23" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="C13" s="23" t="s"/>
-      <x:c r="D13" s="23" t="s"/>
-      <x:c r="E13" s="23" t="s"/>
-      <x:c r="F13" s="24" t="s">
-        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="25" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C14" s="26" t="s"/>
-      <x:c r="D14" s="26" t="s"/>
-      <x:c r="E14" s="26" t="s"/>
-      <x:c r="F14" s="27" t="n">
+      <x:c r="B14" s="26" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="n">
+      <x:c r="B15" s="26" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="28" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="30" t="n">
+      <x:c r="B16" s="29" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -6447,20 +6439,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -6483,249 +6475,249 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="H8" s="17">
+        <x:v>46076.2450058565</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>46076.2450229514</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46076.2450058565</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>46076.2450229514</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K8" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L8" s="18">
+      <x:c r="L8" s="19">
         <x:v>46094.1710418981</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>74</x:v>
+      <x:c r="M8" s="15" t="s">
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
+      <x:c r="B9" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="D9" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
+      <x:c r="E9" s="15" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H9" s="17">
         <x:v>46094.3289943287</x:v>
       </x:c>
-      <x:c r="I9" s="16">
+      <x:c r="I9" s="17">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J9" s="15" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="J9" s="16" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="K9" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="18">
+      <x:c r="L9" s="19">
         <x:v>46107.1436918634</x:v>
       </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="D10" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
+      <x:c r="E10" s="15" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>46094.3273162269</x:v>
       </x:c>
-      <x:c r="I10" s="16">
+      <x:c r="I10" s="17">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="J10" s="16" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L10" s="19">
         <x:v>46107.1513918519</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M10" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
+      <x:c r="B11" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C11" s="14" t="s">
+      <x:c r="D11" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
+      <x:c r="E11" s="15" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
         <x:v>46094.3172049306</x:v>
       </x:c>
-      <x:c r="I11" s="16">
+      <x:c r="I11" s="17">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="J11" s="16" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="18">
+      <x:c r="L11" s="19">
         <x:v>46107.1610127431</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M11" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="19" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C14" s="20" t="s"/>
-      <x:c r="D14" s="20" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="21" t="s"/>
+      <x:c r="B14" s="20" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="22" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="22" t="s">
+      <x:c r="B15" s="23" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="23" t="s"/>
-      <x:c r="F15" s="24" t="s">
-        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="n">
+      <x:c r="B16" s="26" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="n">
+      <x:c r="B17" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="28" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C18" s="29" t="s"/>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="29" t="s"/>
-      <x:c r="F18" s="30" t="n">
+      <x:c r="B18" s="29" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C18" s="30" t="s"/>
+      <x:c r="D18" s="30" t="s"/>
+      <x:c r="E18" s="30" t="s"/>
+      <x:c r="F18" s="31" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-DUANE-NICO-CAWALING-evaluator-cache-serviceTracking-DUANE-NICO-CAWALING-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-DUANE-NICO-CAWALING-evaluator-cache-serviceTracking-DUANE-NICO-CAWALING-IX-202501-202612.xlsx
@@ -319,7 +319,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -359,14 +359,6 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -639,7 +631,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -650,16 +642,13 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -671,53 +660,53 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -752,87 +741,83 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1134,17 +1119,17 @@
       <x:c r="B5" s="12">
         <x:v>45839</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1167,171 +1152,171 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45860.0994011343</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45853</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45860.1449620718</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s"/>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="D9" s="15" t="s"/>
+      <x:c r="E9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>45861.1130539236</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45861.113062963</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>930</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>45862.3035735301</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="19" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="22" t="s"/>
+      <x:c r="C12" s="20" t="s"/>
+      <x:c r="D12" s="20" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="21" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="23" t="s">
+      <x:c r="B13" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="s">
+      <x:c r="C13" s="23" t="s"/>
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="23" t="s"/>
+      <x:c r="F13" s="24" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="26" t="s">
+      <x:c r="B14" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
+      <x:c r="B15" s="25" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
+      <x:c r="B16" s="28" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -2436,17 +2421,17 @@
       <x:c r="B5" s="12">
         <x:v>45870</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2469,222 +2454,222 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45881.2688653125</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45927</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45882.0237933565</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>45870.3069341667</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46186</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>45883.1603418287</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45881.2806375231</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45892</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>45883.297613287</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
+      <x:c r="B13" s="19" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
+      <x:c r="C13" s="20" t="s"/>
+      <x:c r="D13" s="20" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="21" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
+      <x:c r="B14" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="24" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
+      <x:c r="B15" s="25" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
+      <x:c r="B17" s="25" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="29" t="s">
+      <x:c r="B18" s="28" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C18" s="30" t="s"/>
-      <x:c r="D18" s="30" t="s"/>
-      <x:c r="E18" s="30" t="s"/>
-      <x:c r="F18" s="31" t="n">
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -3788,17 +3773,17 @@
       <x:c r="B5" s="12">
         <x:v>45962</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3821,220 +3806,220 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s"/>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="D8" s="15" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45951.1032693866</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45951.1032970718</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45971.088825787</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>45980.216052338</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45979</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>5280</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>45985.3594797917</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45959.0699130787</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>45972.2719636111</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
+      <x:c r="B13" s="19" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
+      <x:c r="C13" s="20" t="s"/>
+      <x:c r="D13" s="20" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="21" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
+      <x:c r="B14" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="24" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
+      <x:c r="B15" s="25" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
+      <x:c r="B17" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="29" t="s">
+      <x:c r="B18" s="28" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C18" s="30" t="s"/>
-      <x:c r="D18" s="30" t="s"/>
-      <x:c r="E18" s="30" t="s"/>
-      <x:c r="F18" s="31" t="n">
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -5138,17 +5123,17 @@
       <x:c r="B5" s="12">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -5171,173 +5156,173 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46057.2343839583</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>41712</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>630</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46072.0668155208</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46066.3781940972</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46081</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46077.0856746296</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="19" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="22" t="s"/>
+      <x:c r="C12" s="20" t="s"/>
+      <x:c r="D12" s="20" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="21" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="23" t="s">
+      <x:c r="B13" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="s">
+      <x:c r="C13" s="23" t="s"/>
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="23" t="s"/>
+      <x:c r="F13" s="24" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="26" t="s">
+      <x:c r="B14" s="25" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
+      <x:c r="B15" s="25" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
+      <x:c r="B16" s="28" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -6442,17 +6427,17 @@
       <x:c r="B5" s="12">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -6475,249 +6460,249 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46076.2450058565</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>46076.2450229514</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46094.1710418981</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46094.3289943287</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46107.1436918634</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>46094.3273162269</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46107.1513918519</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>46094.3172049306</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>46107.1610127431</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="20" t="s">
+      <x:c r="B14" s="19" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="22" t="s"/>
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="21" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+      <x:c r="B15" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="s">
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
+      <x:c r="B17" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="29" t="s">
+      <x:c r="B18" s="28" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C18" s="30" t="s"/>
-      <x:c r="D18" s="30" t="s"/>
-      <x:c r="E18" s="30" t="s"/>
-      <x:c r="F18" s="31" t="n">
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
